--- a/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T10:02:39+00:00</t>
+    <t>2024-03-19T08:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:36:19+00:00</t>
+    <t>2024-04-03T13:59:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>
@@ -347,7 +347,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-mode-fixation-tarifaire</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/VS-TRE-R74-ModeFixationTarifaire</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -689,7 +689,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.31640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="83.71875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:59:51+00:00</t>
+    <t>2024-04-03T14:08:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:18:25+00:00</t>
+    <t>2024-04-03T14:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:35:17+00:00</t>
+    <t>2024-04-03T14:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:54:13+00:00</t>
+    <t>2024-04-08T13:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:06:58+00:00</t>
+    <t>2024-04-08T13:14:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:14:28+00:00</t>
+    <t>2024-04-08T13:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:35:38+00:00</t>
+    <t>2024-04-08T14:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1115,7 +1115,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
@@ -1321,7 +1321,7 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>109</v>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-organization-pricing-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T14:07:36+00:00</t>
+    <t>2024-04-08T14:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
